--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_08-11-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_08-11-2025.xlsx
@@ -592,23 +592,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7dba87a05
-	0x7ff7dba87a60
-	0x7ff7db8016ad
-	0x7ff7db85a13e
-	0x7ff7db85a44c
-	0x7ff7db8aebe7
-	0x7ff7db8ab8fb
-	0x7ff7db84b068
-	0x7ff7db84be93
-	0x7ff7dbd429a0
-	0x7ff7dbd3ce20
-	0x7ff7dbd5cc15
-	0x7ff7dbaa309e
-	0x7ff7dbaaad8f
-	0x7ff7dba90be4
-	0x7ff7dba90d9f
-	0x7ff7dba767f8
+	0x7ff77ca27a05
+	0x7ff77ca27a60
+	0x7ff77c7a16ad
+	0x7ff77c7fa13e
+	0x7ff77c7fa44c
+	0x7ff77c84ebe7
+	0x7ff77c84b8fb
+	0x7ff77c7eb068
+	0x7ff77c7ebe93
+	0x7ff77cce29a0
+	0x7ff77ccdce20
+	0x7ff77ccfcc15
+	0x7ff77ca4309e
+	0x7ff77ca4ad8f
+	0x7ff77ca30be4
+	0x7ff77ca30d9f
+	0x7ff77ca167f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -712,23 +712,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7dba87a05
-	0x7ff7dba87a60
-	0x7ff7db8016ad
-	0x7ff7db85a13e
-	0x7ff7db85a44c
-	0x7ff7db8aebe7
-	0x7ff7db8ab8fb
-	0x7ff7db84b068
-	0x7ff7db84be93
-	0x7ff7dbd429a0
-	0x7ff7dbd3ce20
-	0x7ff7dbd5cc15
-	0x7ff7dbaa309e
-	0x7ff7dbaaad8f
-	0x7ff7dba90be4
-	0x7ff7dba90d9f
-	0x7ff7dba767f8
+	0x7ff77ca27a05
+	0x7ff77ca27a60
+	0x7ff77c7a16ad
+	0x7ff77c7fa13e
+	0x7ff77c7fa44c
+	0x7ff77c84ebe7
+	0x7ff77c84b8fb
+	0x7ff77c7eb068
+	0x7ff77c7ebe93
+	0x7ff77cce29a0
+	0x7ff77ccdce20
+	0x7ff77ccfcc15
+	0x7ff77ca4309e
+	0x7ff77ca4ad8f
+	0x7ff77ca30be4
+	0x7ff77ca30d9f
+	0x7ff77ca167f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -832,23 +832,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7dba87a05
-	0x7ff7dba87a60
-	0x7ff7db8016ad
-	0x7ff7db85a13e
-	0x7ff7db85a44c
-	0x7ff7db8aebe7
-	0x7ff7db8ab8fb
-	0x7ff7db84b068
-	0x7ff7db84be93
-	0x7ff7dbd429a0
-	0x7ff7dbd3ce20
-	0x7ff7dbd5cc15
-	0x7ff7dbaa309e
-	0x7ff7dbaaad8f
-	0x7ff7dba90be4
-	0x7ff7dba90d9f
-	0x7ff7dba767f8
+	0x7ff77ca27a05
+	0x7ff77ca27a60
+	0x7ff77c7a16ad
+	0x7ff77c7fa13e
+	0x7ff77c7fa44c
+	0x7ff77c84ebe7
+	0x7ff77c84b8fb
+	0x7ff77c7eb068
+	0x7ff77c7ebe93
+	0x7ff77cce29a0
+	0x7ff77ccdce20
+	0x7ff77ccfcc15
+	0x7ff77ca4309e
+	0x7ff77ca4ad8f
+	0x7ff77ca30be4
+	0x7ff77ca30d9f
+	0x7ff77ca167f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -952,23 +952,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7dba87a05
-	0x7ff7dba87a60
-	0x7ff7db8016ad
-	0x7ff7db85a13e
-	0x7ff7db85a44c
-	0x7ff7db8aebe7
-	0x7ff7db8ab8fb
-	0x7ff7db84b068
-	0x7ff7db84be93
-	0x7ff7dbd429a0
-	0x7ff7dbd3ce20
-	0x7ff7dbd5cc15
-	0x7ff7dbaa309e
-	0x7ff7dbaaad8f
-	0x7ff7dba90be4
-	0x7ff7dba90d9f
-	0x7ff7dba767f8
+	0x7ff77ca27a05
+	0x7ff77ca27a60
+	0x7ff77c7a16ad
+	0x7ff77c7fa13e
+	0x7ff77c7fa44c
+	0x7ff77c84ebe7
+	0x7ff77c84b8fb
+	0x7ff77c7eb068
+	0x7ff77c7ebe93
+	0x7ff77cce29a0
+	0x7ff77ccdce20
+	0x7ff77ccfcc15
+	0x7ff77ca4309e
+	0x7ff77ca4ad8f
+	0x7ff77ca30be4
+	0x7ff77ca30d9f
+	0x7ff77ca167f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1072,23 +1072,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7dba87a05
-	0x7ff7dba87a60
-	0x7ff7db8016ad
-	0x7ff7db85a13e
-	0x7ff7db85a44c
-	0x7ff7db8aebe7
-	0x7ff7db8ab8fb
-	0x7ff7db84b068
-	0x7ff7db84be93
-	0x7ff7dbd429a0
-	0x7ff7dbd3ce20
-	0x7ff7dbd5cc15
-	0x7ff7dbaa309e
-	0x7ff7dbaaad8f
-	0x7ff7dba90be4
-	0x7ff7dba90d9f
-	0x7ff7dba767f8
+	0x7ff77ca27a05
+	0x7ff77ca27a60
+	0x7ff77c7a16ad
+	0x7ff77c7fa13e
+	0x7ff77c7fa44c
+	0x7ff77c84ebe7
+	0x7ff77c84b8fb
+	0x7ff77c7eb068
+	0x7ff77c7ebe93
+	0x7ff77cce29a0
+	0x7ff77ccdce20
+	0x7ff77ccfcc15
+	0x7ff77ca4309e
+	0x7ff77ca4ad8f
+	0x7ff77ca30be4
+	0x7ff77ca30d9f
+	0x7ff77ca167f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1192,23 +1192,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7dba87a05
-	0x7ff7dba87a60
-	0x7ff7db8016ad
-	0x7ff7db85a13e
-	0x7ff7db85a44c
-	0x7ff7db8aebe7
-	0x7ff7db8ab8fb
-	0x7ff7db84b068
-	0x7ff7db84be93
-	0x7ff7dbd429a0
-	0x7ff7dbd3ce20
-	0x7ff7dbd5cc15
-	0x7ff7dbaa309e
-	0x7ff7dbaaad8f
-	0x7ff7dba90be4
-	0x7ff7dba90d9f
-	0x7ff7dba767f8
+	0x7ff77ca27a05
+	0x7ff77ca27a60
+	0x7ff77c7a16ad
+	0x7ff77c7fa13e
+	0x7ff77c7fa44c
+	0x7ff77c84ebe7
+	0x7ff77c84b8fb
+	0x7ff77c7eb068
+	0x7ff77c7ebe93
+	0x7ff77cce29a0
+	0x7ff77ccdce20
+	0x7ff77ccfcc15
+	0x7ff77ca4309e
+	0x7ff77ca4ad8f
+	0x7ff77ca30be4
+	0x7ff77ca30d9f
+	0x7ff77ca167f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1312,23 +1312,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7dba87a05
-	0x7ff7dba87a60
-	0x7ff7db8016ad
-	0x7ff7db85a13e
-	0x7ff7db85a44c
-	0x7ff7db8aebe7
-	0x7ff7db8ab8fb
-	0x7ff7db84b068
-	0x7ff7db84be93
-	0x7ff7dbd429a0
-	0x7ff7dbd3ce20
-	0x7ff7dbd5cc15
-	0x7ff7dbaa309e
-	0x7ff7dbaaad8f
-	0x7ff7dba90be4
-	0x7ff7dba90d9f
-	0x7ff7dba767f8
+	0x7ff77ca27a05
+	0x7ff77ca27a60
+	0x7ff77c7a16ad
+	0x7ff77c7fa13e
+	0x7ff77c7fa44c
+	0x7ff77c84ebe7
+	0x7ff77c84b8fb
+	0x7ff77c7eb068
+	0x7ff77c7ebe93
+	0x7ff77cce29a0
+	0x7ff77ccdce20
+	0x7ff77ccfcc15
+	0x7ff77ca4309e
+	0x7ff77ca4ad8f
+	0x7ff77ca30be4
+	0x7ff77ca30d9f
+	0x7ff77ca167f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1432,23 +1432,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7dba87a05
-	0x7ff7dba87a60
-	0x7ff7db8016ad
-	0x7ff7db85a13e
-	0x7ff7db85a44c
-	0x7ff7db8aebe7
-	0x7ff7db8ab8fb
-	0x7ff7db84b068
-	0x7ff7db84be93
-	0x7ff7dbd429a0
-	0x7ff7dbd3ce20
-	0x7ff7dbd5cc15
-	0x7ff7dbaa309e
-	0x7ff7dbaaad8f
-	0x7ff7dba90be4
-	0x7ff7dba90d9f
-	0x7ff7dba767f8
+	0x7ff77ca27a05
+	0x7ff77ca27a60
+	0x7ff77c7a16ad
+	0x7ff77c7fa13e
+	0x7ff77c7fa44c
+	0x7ff77c84ebe7
+	0x7ff77c84b8fb
+	0x7ff77c7eb068
+	0x7ff77c7ebe93
+	0x7ff77cce29a0
+	0x7ff77ccdce20
+	0x7ff77ccfcc15
+	0x7ff77ca4309e
+	0x7ff77ca4ad8f
+	0x7ff77ca30be4
+	0x7ff77ca30d9f
+	0x7ff77ca167f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1552,23 +1552,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7dba87a05
-	0x7ff7dba87a60
-	0x7ff7db8016ad
-	0x7ff7db85a13e
-	0x7ff7db85a44c
-	0x7ff7db8aebe7
-	0x7ff7db8ab8fb
-	0x7ff7db84b068
-	0x7ff7db84be93
-	0x7ff7dbd429a0
-	0x7ff7dbd3ce20
-	0x7ff7dbd5cc15
-	0x7ff7dbaa309e
-	0x7ff7dbaaad8f
-	0x7ff7dba90be4
-	0x7ff7dba90d9f
-	0x7ff7dba767f8
+	0x7ff77ca27a05
+	0x7ff77ca27a60
+	0x7ff77c7a16ad
+	0x7ff77c7fa13e
+	0x7ff77c7fa44c
+	0x7ff77c84ebe7
+	0x7ff77c84b8fb
+	0x7ff77c7eb068
+	0x7ff77c7ebe93
+	0x7ff77cce29a0
+	0x7ff77ccdce20
+	0x7ff77ccfcc15
+	0x7ff77ca4309e
+	0x7ff77ca4ad8f
+	0x7ff77ca30be4
+	0x7ff77ca30d9f
+	0x7ff77ca167f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1672,23 +1672,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7dba87a05
-	0x7ff7dba87a60
-	0x7ff7db8016ad
-	0x7ff7db85a13e
-	0x7ff7db85a44c
-	0x7ff7db8aebe7
-	0x7ff7db8ab8fb
-	0x7ff7db84b068
-	0x7ff7db84be93
-	0x7ff7dbd429a0
-	0x7ff7dbd3ce20
-	0x7ff7dbd5cc15
-	0x7ff7dbaa309e
-	0x7ff7dbaaad8f
-	0x7ff7dba90be4
-	0x7ff7dba90d9f
-	0x7ff7dba767f8
+	0x7ff77ca27a05
+	0x7ff77ca27a60
+	0x7ff77c7a16ad
+	0x7ff77c7fa13e
+	0x7ff77c7fa44c
+	0x7ff77c84ebe7
+	0x7ff77c84b8fb
+	0x7ff77c7eb068
+	0x7ff77c7ebe93
+	0x7ff77cce29a0
+	0x7ff77ccdce20
+	0x7ff77ccfcc15
+	0x7ff77ca4309e
+	0x7ff77ca4ad8f
+	0x7ff77ca30be4
+	0x7ff77ca30d9f
+	0x7ff77ca167f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1792,23 +1792,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7dba87a05
-	0x7ff7dba87a60
-	0x7ff7db8016ad
-	0x7ff7db85a13e
-	0x7ff7db85a44c
-	0x7ff7db8aebe7
-	0x7ff7db8ab8fb
-	0x7ff7db84b068
-	0x7ff7db84be93
-	0x7ff7dbd429a0
-	0x7ff7dbd3ce20
-	0x7ff7dbd5cc15
-	0x7ff7dbaa309e
-	0x7ff7dbaaad8f
-	0x7ff7dba90be4
-	0x7ff7dba90d9f
-	0x7ff7dba767f8
+	0x7ff77ca27a05
+	0x7ff77ca27a60
+	0x7ff77c7a16ad
+	0x7ff77c7fa13e
+	0x7ff77c7fa44c
+	0x7ff77c84ebe7
+	0x7ff77c84b8fb
+	0x7ff77c7eb068
+	0x7ff77c7ebe93
+	0x7ff77cce29a0
+	0x7ff77ccdce20
+	0x7ff77ccfcc15
+	0x7ff77ca4309e
+	0x7ff77ca4ad8f
+	0x7ff77ca30be4
+	0x7ff77ca30d9f
+	0x7ff77ca167f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1912,23 +1912,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7dba87a05
-	0x7ff7dba87a60
-	0x7ff7db8016ad
-	0x7ff7db85a13e
-	0x7ff7db85a44c
-	0x7ff7db8aebe7
-	0x7ff7db8ab8fb
-	0x7ff7db84b068
-	0x7ff7db84be93
-	0x7ff7dbd429a0
-	0x7ff7dbd3ce20
-	0x7ff7dbd5cc15
-	0x7ff7dbaa309e
-	0x7ff7dbaaad8f
-	0x7ff7dba90be4
-	0x7ff7dba90d9f
-	0x7ff7dba767f8
+	0x7ff77ca27a05
+	0x7ff77ca27a60
+	0x7ff77c7a16ad
+	0x7ff77c7fa13e
+	0x7ff77c7fa44c
+	0x7ff77c84ebe7
+	0x7ff77c84b8fb
+	0x7ff77c7eb068
+	0x7ff77c7ebe93
+	0x7ff77cce29a0
+	0x7ff77ccdce20
+	0x7ff77ccfcc15
+	0x7ff77ca4309e
+	0x7ff77ca4ad8f
+	0x7ff77ca30be4
+	0x7ff77ca30d9f
+	0x7ff77ca167f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -2032,23 +2032,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7dba87a05
-	0x7ff7dba87a60
-	0x7ff7db8016ad
-	0x7ff7db85a13e
-	0x7ff7db85a44c
-	0x7ff7db8aebe7
-	0x7ff7db8ab8fb
-	0x7ff7db84b068
-	0x7ff7db84be93
-	0x7ff7dbd429a0
-	0x7ff7dbd3ce20
-	0x7ff7dbd5cc15
-	0x7ff7dbaa309e
-	0x7ff7dbaaad8f
-	0x7ff7dba90be4
-	0x7ff7dba90d9f
-	0x7ff7dba767f8
+	0x7ff77ca27a05
+	0x7ff77ca27a60
+	0x7ff77c7a16ad
+	0x7ff77c7fa13e
+	0x7ff77c7fa44c
+	0x7ff77c84ebe7
+	0x7ff77c84b8fb
+	0x7ff77c7eb068
+	0x7ff77c7ebe93
+	0x7ff77cce29a0
+	0x7ff77ccdce20
+	0x7ff77ccfcc15
+	0x7ff77ca4309e
+	0x7ff77ca4ad8f
+	0x7ff77ca30be4
+	0x7ff77ca30d9f
+	0x7ff77ca167f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -2152,23 +2152,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7dba87a05
-	0x7ff7dba87a60
-	0x7ff7db8016ad
-	0x7ff7db85a13e
-	0x7ff7db85a44c
-	0x7ff7db8aebe7
-	0x7ff7db8ab8fb
-	0x7ff7db84b068
-	0x7ff7db84be93
-	0x7ff7dbd429a0
-	0x7ff7dbd3ce20
-	0x7ff7dbd5cc15
-	0x7ff7dbaa309e
-	0x7ff7dbaaad8f
-	0x7ff7dba90be4
-	0x7ff7dba90d9f
-	0x7ff7dba767f8
+	0x7ff77ca27a05
+	0x7ff77ca27a60
+	0x7ff77c7a16ad
+	0x7ff77c7fa13e
+	0x7ff77c7fa44c
+	0x7ff77c84ebe7
+	0x7ff77c84b8fb
+	0x7ff77c7eb068
+	0x7ff77c7ebe93
+	0x7ff77cce29a0
+	0x7ff77ccdce20
+	0x7ff77ccfcc15
+	0x7ff77ca4309e
+	0x7ff77ca4ad8f
+	0x7ff77ca30be4
+	0x7ff77ca30d9f
+	0x7ff77ca167f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -2272,23 +2272,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7dba87a05
-	0x7ff7dba87a60
-	0x7ff7db8016ad
-	0x7ff7db85a13e
-	0x7ff7db85a44c
-	0x7ff7db8aebe7
-	0x7ff7db8ab8fb
-	0x7ff7db84b068
-	0x7ff7db84be93
-	0x7ff7dbd429a0
-	0x7ff7dbd3ce20
-	0x7ff7dbd5cc15
-	0x7ff7dbaa309e
-	0x7ff7dbaaad8f
-	0x7ff7dba90be4
-	0x7ff7dba90d9f
-	0x7ff7dba767f8
+	0x7ff77ca27a05
+	0x7ff77ca27a60
+	0x7ff77c7a16ad
+	0x7ff77c7fa13e
+	0x7ff77c7fa44c
+	0x7ff77c84ebe7
+	0x7ff77c84b8fb
+	0x7ff77c7eb068
+	0x7ff77c7ebe93
+	0x7ff77cce29a0
+	0x7ff77ccdce20
+	0x7ff77ccfcc15
+	0x7ff77ca4309e
+	0x7ff77ca4ad8f
+	0x7ff77ca30be4
+	0x7ff77ca30d9f
+	0x7ff77ca167f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -2489,23 +2489,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7dba87a05
-	0x7ff7dba87a60
-	0x7ff7db8016ad
-	0x7ff7db85a13e
-	0x7ff7db85a44c
-	0x7ff7db8aebe7
-	0x7ff7db8ab8fb
-	0x7ff7db84b068
-	0x7ff7db84be93
-	0x7ff7dbd429a0
-	0x7ff7dbd3ce20
-	0x7ff7dbd5cc15
-	0x7ff7dbaa309e
-	0x7ff7dbaaad8f
-	0x7ff7dba90be4
-	0x7ff7dba90d9f
-	0x7ff7dba767f8
+	0x7ff77ca27a05
+	0x7ff77ca27a60
+	0x7ff77c7a16ad
+	0x7ff77c7fa13e
+	0x7ff77c7fa44c
+	0x7ff77c84ebe7
+	0x7ff77c84b8fb
+	0x7ff77c7eb068
+	0x7ff77c7ebe93
+	0x7ff77cce29a0
+	0x7ff77ccdce20
+	0x7ff77ccfcc15
+	0x7ff77ca4309e
+	0x7ff77ca4ad8f
+	0x7ff77ca30be4
+	0x7ff77ca30d9f
+	0x7ff77ca167f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -2609,23 +2609,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7dba87a05
-	0x7ff7dba87a60
-	0x7ff7db8016ad
-	0x7ff7db85a13e
-	0x7ff7db85a44c
-	0x7ff7db8aebe7
-	0x7ff7db8ab8fb
-	0x7ff7db84b068
-	0x7ff7db84be93
-	0x7ff7dbd429a0
-	0x7ff7dbd3ce20
-	0x7ff7dbd5cc15
-	0x7ff7dbaa309e
-	0x7ff7dbaaad8f
-	0x7ff7dba90be4
-	0x7ff7dba90d9f
-	0x7ff7dba767f8
+	0x7ff77ca27a05
+	0x7ff77ca27a60
+	0x7ff77c7a16ad
+	0x7ff77c7fa13e
+	0x7ff77c7fa44c
+	0x7ff77c84ebe7
+	0x7ff77c84b8fb
+	0x7ff77c7eb068
+	0x7ff77c7ebe93
+	0x7ff77cce29a0
+	0x7ff77ccdce20
+	0x7ff77ccfcc15
+	0x7ff77ca4309e
+	0x7ff77ca4ad8f
+	0x7ff77ca30be4
+	0x7ff77ca30d9f
+	0x7ff77ca167f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -2729,23 +2729,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7dba87a05
-	0x7ff7dba87a60
-	0x7ff7db8016ad
-	0x7ff7db85a13e
-	0x7ff7db85a44c
-	0x7ff7db8aebe7
-	0x7ff7db8ab8fb
-	0x7ff7db84b068
-	0x7ff7db84be93
-	0x7ff7dbd429a0
-	0x7ff7dbd3ce20
-	0x7ff7dbd5cc15
-	0x7ff7dbaa309e
-	0x7ff7dbaaad8f
-	0x7ff7dba90be4
-	0x7ff7dba90d9f
-	0x7ff7dba767f8
+	0x7ff77ca27a05
+	0x7ff77ca27a60
+	0x7ff77c7a16ad
+	0x7ff77c7fa13e
+	0x7ff77c7fa44c
+	0x7ff77c84ebe7
+	0x7ff77c84b8fb
+	0x7ff77c7eb068
+	0x7ff77c7ebe93
+	0x7ff77cce29a0
+	0x7ff77ccdce20
+	0x7ff77ccfcc15
+	0x7ff77ca4309e
+	0x7ff77ca4ad8f
+	0x7ff77ca30be4
+	0x7ff77ca30d9f
+	0x7ff77ca167f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -2849,23 +2849,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7dba87a05
-	0x7ff7dba87a60
-	0x7ff7db8016ad
-	0x7ff7db85a13e
-	0x7ff7db85a44c
-	0x7ff7db8aebe7
-	0x7ff7db8ab8fb
-	0x7ff7db84b068
-	0x7ff7db84be93
-	0x7ff7dbd429a0
-	0x7ff7dbd3ce20
-	0x7ff7dbd5cc15
-	0x7ff7dbaa309e
-	0x7ff7dbaaad8f
-	0x7ff7dba90be4
-	0x7ff7dba90d9f
-	0x7ff7dba767f8
+	0x7ff77ca27a05
+	0x7ff77ca27a60
+	0x7ff77c7a16ad
+	0x7ff77c7fa13e
+	0x7ff77c7fa44c
+	0x7ff77c84ebe7
+	0x7ff77c84b8fb
+	0x7ff77c7eb068
+	0x7ff77c7ebe93
+	0x7ff77cce29a0
+	0x7ff77ccdce20
+	0x7ff77ccfcc15
+	0x7ff77ca4309e
+	0x7ff77ca4ad8f
+	0x7ff77ca30be4
+	0x7ff77ca30d9f
+	0x7ff77ca167f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -2969,23 +2969,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7dba87a05
-	0x7ff7dba87a60
-	0x7ff7db8016ad
-	0x7ff7db85a13e
-	0x7ff7db85a44c
-	0x7ff7db8aebe7
-	0x7ff7db8ab8fb
-	0x7ff7db84b068
-	0x7ff7db84be93
-	0x7ff7dbd429a0
-	0x7ff7dbd3ce20
-	0x7ff7dbd5cc15
-	0x7ff7dbaa309e
-	0x7ff7dbaaad8f
-	0x7ff7dba90be4
-	0x7ff7dba90d9f
-	0x7ff7dba767f8
+	0x7ff77ca27a05
+	0x7ff77ca27a60
+	0x7ff77c7a16ad
+	0x7ff77c7fa13e
+	0x7ff77c7fa44c
+	0x7ff77c84ebe7
+	0x7ff77c84b8fb
+	0x7ff77c7eb068
+	0x7ff77c7ebe93
+	0x7ff77cce29a0
+	0x7ff77ccdce20
+	0x7ff77ccfcc15
+	0x7ff77ca4309e
+	0x7ff77ca4ad8f
+	0x7ff77ca30be4
+	0x7ff77ca30d9f
+	0x7ff77ca167f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -3089,23 +3089,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7dba87a05
-	0x7ff7dba87a60
-	0x7ff7db8016ad
-	0x7ff7db85a13e
-	0x7ff7db85a44c
-	0x7ff7db8aebe7
-	0x7ff7db8ab8fb
-	0x7ff7db84b068
-	0x7ff7db84be93
-	0x7ff7dbd429a0
-	0x7ff7dbd3ce20
-	0x7ff7dbd5cc15
-	0x7ff7dbaa309e
-	0x7ff7dbaaad8f
-	0x7ff7dba90be4
-	0x7ff7dba90d9f
-	0x7ff7dba767f8
+	0x7ff77ca27a05
+	0x7ff77ca27a60
+	0x7ff77c7a16ad
+	0x7ff77c7fa13e
+	0x7ff77c7fa44c
+	0x7ff77c84ebe7
+	0x7ff77c84b8fb
+	0x7ff77c7eb068
+	0x7ff77c7ebe93
+	0x7ff77cce29a0
+	0x7ff77ccdce20
+	0x7ff77ccfcc15
+	0x7ff77ca4309e
+	0x7ff77ca4ad8f
+	0x7ff77ca30be4
+	0x7ff77ca30d9f
+	0x7ff77ca167f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -3209,23 +3209,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7dba87a05
-	0x7ff7dba87a60
-	0x7ff7db8016ad
-	0x7ff7db85a13e
-	0x7ff7db85a44c
-	0x7ff7db8aebe7
-	0x7ff7db8ab8fb
-	0x7ff7db84b068
-	0x7ff7db84be93
-	0x7ff7dbd429a0
-	0x7ff7dbd3ce20
-	0x7ff7dbd5cc15
-	0x7ff7dbaa309e
-	0x7ff7dbaaad8f
-	0x7ff7dba90be4
-	0x7ff7dba90d9f
-	0x7ff7dba767f8
+	0x7ff77ca27a05
+	0x7ff77ca27a60
+	0x7ff77c7a16ad
+	0x7ff77c7fa13e
+	0x7ff77c7fa44c
+	0x7ff77c84ebe7
+	0x7ff77c84b8fb
+	0x7ff77c7eb068
+	0x7ff77c7ebe93
+	0x7ff77cce29a0
+	0x7ff77ccdce20
+	0x7ff77ccfcc15
+	0x7ff77ca4309e
+	0x7ff77ca4ad8f
+	0x7ff77ca30be4
+	0x7ff77ca30d9f
+	0x7ff77ca167f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -3329,23 +3329,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7dba87a05
-	0x7ff7dba87a60
-	0x7ff7db8016ad
-	0x7ff7db85a13e
-	0x7ff7db85a44c
-	0x7ff7db8aebe7
-	0x7ff7db8ab8fb
-	0x7ff7db84b068
-	0x7ff7db84be93
-	0x7ff7dbd429a0
-	0x7ff7dbd3ce20
-	0x7ff7dbd5cc15
-	0x7ff7dbaa309e
-	0x7ff7dbaaad8f
-	0x7ff7dba90be4
-	0x7ff7dba90d9f
-	0x7ff7dba767f8
+	0x7ff77ca27a05
+	0x7ff77ca27a60
+	0x7ff77c7a16ad
+	0x7ff77c7fa13e
+	0x7ff77c7fa44c
+	0x7ff77c84ebe7
+	0x7ff77c84b8fb
+	0x7ff77c7eb068
+	0x7ff77c7ebe93
+	0x7ff77cce29a0
+	0x7ff77ccdce20
+	0x7ff77ccfcc15
+	0x7ff77ca4309e
+	0x7ff77ca4ad8f
+	0x7ff77ca30be4
+	0x7ff77ca30d9f
+	0x7ff77ca167f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -3449,23 +3449,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7dba87a05
-	0x7ff7dba87a60
-	0x7ff7db8016ad
-	0x7ff7db85a13e
-	0x7ff7db85a44c
-	0x7ff7db8aebe7
-	0x7ff7db8ab8fb
-	0x7ff7db84b068
-	0x7ff7db84be93
-	0x7ff7dbd429a0
-	0x7ff7dbd3ce20
-	0x7ff7dbd5cc15
-	0x7ff7dbaa309e
-	0x7ff7dbaaad8f
-	0x7ff7dba90be4
-	0x7ff7dba90d9f
-	0x7ff7dba767f8
+	0x7ff77ca27a05
+	0x7ff77ca27a60
+	0x7ff77c7a16ad
+	0x7ff77c7fa13e
+	0x7ff77c7fa44c
+	0x7ff77c84ebe7
+	0x7ff77c84b8fb
+	0x7ff77c7eb068
+	0x7ff77c7ebe93
+	0x7ff77cce29a0
+	0x7ff77ccdce20
+	0x7ff77ccfcc15
+	0x7ff77ca4309e
+	0x7ff77ca4ad8f
+	0x7ff77ca30be4
+	0x7ff77ca30d9f
+	0x7ff77ca167f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
